--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_advertencias/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_advertencias/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DAE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="ADVERTENCIAS_ESPERADAS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADVERTENCIAS_ESPERADAS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_advertencias/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_advertencias/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -270,7 +270,7 @@
         <t>ID del Niño, niña o Adolescente
 Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -626,7 +626,7 @@
       <text>
         <t>ID del Niño, niña o Adolescente
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -1326,9 +1326,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>42.84</v>
       </c>
       <c r="AI4" s="5" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>29.65</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>87.76000000000001</v>
       </c>
       <c r="AI6" s="5" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>45590</v>
+        <v>45591</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>38.78</v>
       </c>
       <c r="AI7" s="5" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>33.09</v>
       </c>
       <c r="AI8" s="5" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>34.47</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45870</v>
+        <v>45871</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>43.67</v>
       </c>
       <c r="AI10" s="5" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>41.23</v>
       </c>
       <c r="AI11" s="5" t="n">
-        <v>45857</v>
+        <v>45858</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>19.4</v>
       </c>
       <c r="AI12" s="5" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>99.61</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46015</v>
+        <v>46016</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45720</v>
+        <v>45721</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>21.85</v>
       </c>
       <c r="AI14" s="5" t="n">
-        <v>45808</v>
+        <v>45809</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45786</v>
+        <v>45787</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45728</v>
+        <v>45729</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>15.66</v>
       </c>
       <c r="AI15" s="5" t="n">
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>20.76</v>
       </c>
       <c r="AI16" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>39.13</v>
       </c>
       <c r="AI17" s="5" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46597</v>
+        <v>46598</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>29.4</v>
       </c>
       <c r="AI18" s="5" t="n">
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>72.12</v>
       </c>
       <c r="AI19" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>25.48</v>
       </c>
       <c r="AI20" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="N21" s="5" t="n">
-        <v>46376</v>
+        <v>46377</v>
       </c>
       <c r="O21" s="6" t="n">
         <v>99</v>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>34.28</v>
       </c>
       <c r="AI21" s="5" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45808</v>
+        <v>45809</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>54.4</v>
       </c>
       <c r="AI22" s="5" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>68.06</v>
       </c>
       <c r="AI23" s="5" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45843</v>
+        <v>45844</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>16.15</v>
       </c>
       <c r="AI24" s="5" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>88.15000000000001</v>
       </c>
       <c r="AI25" s="5" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45757</v>
+        <v>45758</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>35.83</v>
       </c>
       <c r="AI26" s="5" t="n">
-        <v>45860</v>
+        <v>45861</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>2.21</v>
       </c>
       <c r="AI27" s="5" t="n">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45982</v>
+        <v>45983</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>62.48</v>
       </c>
       <c r="AI28" s="5" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>54.91</v>
       </c>
       <c r="AI29" s="5" t="n">
-        <v>45849</v>
+        <v>45850</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45697</v>
+        <v>45698</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>4.98</v>
       </c>
       <c r="AI30" s="5" t="n">
-        <v>45891</v>
+        <v>45892</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="AI31" s="5" t="n">
-        <v>45941</v>
+        <v>45942</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45760</v>
+        <v>45761</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>55.67</v>
       </c>
       <c r="AI32" s="5" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>59.11</v>
       </c>
       <c r="AI33" s="5" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -8164,9 +8164,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -8352,7 +8352,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45730</v>
+        <v>45731</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="AD4" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="AK4" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -8534,7 +8534,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="AD5" s="8" t="n">
         <v>0.4791666666666667</v>
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>0.7395833333333334</v>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="N6" s="5" t="n">
-        <v>46385</v>
+        <v>46386</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>17</v>
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>45977</v>
+        <v>45978</v>
       </c>
       <c r="AD6" s="8" t="n">
         <v>0.53125</v>
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="AK6" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>45835</v>
+        <v>45836</v>
       </c>
       <c r="AD7" s="8" t="n">
         <v>0.3125</v>
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>45942</v>
+        <v>45943</v>
       </c>
       <c r="AK7" s="8" t="n">
         <v>0.46875</v>
@@ -9123,7 +9123,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>45821</v>
+        <v>45822</v>
       </c>
       <c r="AD8" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
-        <v>45942</v>
+        <v>45943</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>0.2708333333333333</v>
@@ -9310,7 +9310,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="AD9" s="8" t="n">
         <v>0.90625</v>
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK9" s="8" t="n">
         <v>0.5625</v>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="AM9" s="13" t="n">
-        <v>46652</v>
+        <v>46653</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>45821</v>
+        <v>45822</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="AD10" s="8" t="n">
         <v>0.9791666666666666</v>
@@ -9656,7 +9656,7 @@
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="AK10" s="8" t="n">
         <v>0.5625</v>
@@ -9688,7 +9688,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45855</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>45850</v>
+        <v>45851</v>
       </c>
       <c r="AD11" s="8" t="n">
         <v>0.40625</v>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="AK11" s="8" t="n">
         <v>0.34375</v>
@@ -9887,7 +9887,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="AD12" s="8" t="n">
         <v>0.6041666666666666</v>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
-        <v>45990</v>
+        <v>45991</v>
       </c>
       <c r="AK12" s="8" t="n">
         <v>0.7916666666666666</v>
@@ -10082,7 +10082,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>45711</v>
+        <v>45712</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="AD13" s="8" t="n">
         <v>0.3958333333333333</v>
@@ -10241,7 +10241,7 @@
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="AK13" s="8" t="n">
         <v>0.9583333333333334</v>
@@ -10273,7 +10273,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45954</v>
+        <v>45955</v>
       </c>
       <c r="AD14" s="8" t="n">
         <v>0.3333333333333333</v>
@@ -10427,7 +10427,7 @@
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="AK14" s="8" t="n">
         <v>0.6145833333333334</v>
@@ -10455,7 +10455,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AD15" s="8" t="n">
         <v>0.90625</v>
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
-        <v>46658</v>
+        <v>46659</v>
       </c>
       <c r="AK15" s="8" t="n">
         <v>0.75</v>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45697</v>
+        <v>45698</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="AD16" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -10805,7 +10805,7 @@
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="AK16" s="8" t="n">
         <v>0.3854166666666667</v>
@@ -10833,7 +10833,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="AD17" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="AK17" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -11024,7 +11024,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>45837</v>
+        <v>45838</v>
       </c>
       <c r="AD18" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -11182,10 +11182,10 @@
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AK18" s="8" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AD19" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -11372,7 +11372,7 @@
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
-        <v>45802</v>
+        <v>45803</v>
       </c>
       <c r="AK19" s="8" t="n">
         <v>0.6979166666666666</v>
@@ -11400,7 +11400,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>45970</v>
+        <v>45971</v>
       </c>
       <c r="AD20" s="8" t="n">
         <v>0.8854166666666666</v>
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="AK20" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -11586,7 +11586,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>45794</v>
+        <v>45795</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="AD21" s="8" t="n">
         <v>0.5729166666666666</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="AK21" s="8" t="n">
         <v>0.6770833333333334</v>
@@ -11756,7 +11756,7 @@
         </is>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>46665</v>
+        <v>46666</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="AD22" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
-        <v>45730</v>
+        <v>45731</v>
       </c>
       <c r="AK22" s="8" t="n">
         <v>0.5729166666666666</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="AD23" s="8" t="n">
         <v>0.9791666666666666</v>
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
-        <v>45961</v>
+        <v>45962</v>
       </c>
       <c r="AK23" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -12152,7 +12152,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45969</v>
+        <v>45970</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="AD24" s="8" t="n">
         <v>0.90625</v>
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="AK24" s="8" t="n">
         <v>0.8020833333333334</v>
@@ -12343,7 +12343,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45610</v>
+        <v>45611</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45591</v>
+        <v>45592</v>
       </c>
       <c r="AD25" s="8" t="n">
         <v>0.4583333333333333</v>
@@ -12501,7 +12501,7 @@
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="AK25" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -12537,7 +12537,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45830</v>
+        <v>45831</v>
       </c>
       <c r="AD26" s="8" t="n">
         <v>0.5208333333333334</v>
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="AJ26" s="5" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="AK26" s="8" t="n">
         <v>0.4895833333333333</v>
@@ -12727,7 +12727,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>45796</v>
+        <v>45797</v>
       </c>
       <c r="AD27" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="AJ27" s="5" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="AK27" s="8" t="n">
         <v>0.4270833333333333</v>
@@ -12909,7 +12909,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45756</v>
+        <v>45757</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45680</v>
+        <v>45681</v>
       </c>
       <c r="AD28" s="8" t="n">
         <v>0.4270833333333333</v>
@@ -13067,7 +13067,7 @@
         </is>
       </c>
       <c r="AJ28" s="5" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="AK28" s="8" t="n">
         <v>0.59375</v>
@@ -13099,7 +13099,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>45728</v>
+        <v>45729</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45933</v>
+        <v>45934</v>
       </c>
       <c r="AD29" s="8" t="n">
         <v>0.7604166666666666</v>
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="AJ29" s="5" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="AK29" s="8" t="n">
         <v>0.6145833333333334</v>
@@ -13285,7 +13285,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45912</v>
+        <v>45913</v>
       </c>
       <c r="AD30" s="8" t="n">
         <v>0.7708333333333334</v>
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
-        <v>45962</v>
+        <v>45963</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -13476,7 +13476,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="AD31" s="8" t="n">
         <v>0.84375</v>
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="AJ31" s="5" t="n">
-        <v>45856</v>
+        <v>45857</v>
       </c>
       <c r="AK31" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -13671,7 +13671,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="AD32" s="8" t="n">
         <v>0.7604166666666666</v>
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="AJ32" s="5" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="AK32" s="8" t="n">
         <v>0.28125</v>
@@ -13858,7 +13858,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>45804</v>
+        <v>45805</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="AD33" s="8" t="n">
         <v>0.5625</v>
@@ -14012,10 +14012,10 @@
         </is>
       </c>
       <c r="AJ33" s="5" t="n">
-        <v>46560</v>
+        <v>46561</v>
       </c>
       <c r="AK33" s="8" t="n">
-        <v>46497</v>
+        <v>46498</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -16115,7 +16115,8 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.</t>
+          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
+Campo obligatorio.</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16621,11 @@
           <t>ID del Niño, niña o Adolescente</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Campo obligatorio.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
